--- a/input_data/input_data_bidcurve_e.xlsx
+++ b/input_data/input_data_bidcurve_e.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sovelluskehitys\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D17454F-FC20-4ED0-A7C7-4C17A030C745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4037A505-A8B9-4C65-8B9E-834EE7A836F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8964" tabRatio="796" firstSheet="14" activeTab="21" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20595" windowHeight="13455" tabRatio="796" firstSheet="8" activeTab="21" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="18" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="315">
   <si>
     <t>node</t>
   </si>
@@ -314,9 +314,6 @@
     <t>use_market_bids</t>
   </si>
   <si>
-    <t>common_timesteps</t>
-  </si>
-  <si>
     <t>common_scenario_name</t>
   </si>
   <si>
@@ -1002,6 +999,12 @@
   </si>
   <si>
     <t>group_type</t>
+  </si>
+  <si>
+    <t>common_start_timesteps</t>
+  </si>
+  <si>
+    <t>common_end_timesteps</t>
   </si>
 </sst>
 </file>
@@ -1380,178 +1383,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39053E69-3A75-490E-847C-66A9CF6C1FC5}">
   <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>44671.208333333336</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>44671.25</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>44671.291666666664</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>44671.333333333336</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>44671.375</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>44671.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>44671.458333333336</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="7"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="7"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="7"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="7"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="7"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="7"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="7"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="7"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="7"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="7"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="7"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="7"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="7"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="7"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="7"/>
     </row>
   </sheetData>
@@ -1562,157 +1565,157 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA355BEF-1F4B-494A-B089-4FCDFFFA57F7}">
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.208333333336</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.25</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.291666666664</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.333333333336</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.375</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.458333333336</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -1727,9 +1730,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0532F8A-0FB4-47AD-98A1-4065D3376432}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>42</v>
       </c>
@@ -1745,20 +1748,20 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A4637A-7829-48D6-AE54-2E654AB1A427}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="23.109375" customWidth="1"/>
-    <col min="12" max="12" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671.08333321759</v>
@@ -1766,139 +1769,139 @@
       <c r="F2" s="7"/>
       <c r="L2" s="7"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.208333333336</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.25</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.291666666664</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.333333333336</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.375</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.458333333336</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -1914,19 +1917,19 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F87DD44-A1AD-4241-AED7-C48CC9DEE2E2}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="7" customWidth="1"/>
-    <col min="4" max="6" width="10.44140625" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
+    <col min="4" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671.08333321759</v>
@@ -1934,7 +1937,7 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.124999826388</v>
@@ -1942,7 +1945,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.166666435187</v>
@@ -1950,7 +1953,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.208333333336</v>
@@ -1958,7 +1961,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.25</v>
@@ -1966,7 +1969,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.291666666664</v>
@@ -1974,7 +1977,7 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.333333333336</v>
@@ -1982,7 +1985,7 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.375</v>
@@ -1990,7 +1993,7 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.416666666664</v>
@@ -1998,7 +2001,7 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.458333333336</v>
@@ -2006,7 +2009,7 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
@@ -2014,7 +2017,7 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
@@ -2022,7 +2025,7 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
@@ -2030,7 +2033,7 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
@@ -2038,7 +2041,7 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
@@ -2046,7 +2049,7 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
@@ -2054,7 +2057,7 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
@@ -2062,7 +2065,7 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
@@ -2070,7 +2073,7 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
@@ -2078,7 +2081,7 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
@@ -2086,7 +2089,7 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
@@ -2094,7 +2097,7 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
@@ -2102,7 +2105,7 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
@@ -2110,7 +2113,7 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -2128,82 +2131,82 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098BD40C-3F1E-4DCA-B153-EDE213641CC0}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="3" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="C2" s="7"/>
       <c r="E2" s="7"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="C3" s="7"/>
       <c r="E3" s="7"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="C4" s="7"/>
       <c r="E4" s="7"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="C5" s="7"/>
       <c r="E5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
@@ -2217,20 +2220,20 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02307C1F-427B-487D-B703-EBF512D7AC27}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671.08333321759</v>
@@ -2239,7 +2242,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.124999826388</v>
@@ -2248,7 +2251,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.166666435187</v>
@@ -2257,7 +2260,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.208333333336</v>
@@ -2266,7 +2269,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.25</v>
@@ -2275,7 +2278,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.291666666664</v>
@@ -2284,7 +2287,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.333333333336</v>
@@ -2293,7 +2296,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.375</v>
@@ -2302,7 +2305,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.416666666664</v>
@@ -2311,7 +2314,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.458333333336</v>
@@ -2320,85 +2323,85 @@
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -2412,22 +2415,22 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3788A93-7501-4F5D-9E8F-38D329CC85EC}">
   <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -2457,7 +2460,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
@@ -2492,7 +2495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2503,7 +2506,7 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2514,7 +2517,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -2533,156 +2536,156 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21372C5-DB60-4318-868D-D4FA20FECD5D}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="7" customWidth="1"/>
-    <col min="2" max="3" width="6.5546875" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
+    <col min="2" max="3" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.208333333336</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.25</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.291666666664</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.333333333336</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.375</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.458333333336</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -2696,50 +2699,50 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D78009B3-2276-4B8E-8066-7570B2DF617B}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1" t="s">
         <v>297</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>298</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>299</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>300</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>301</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>302</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>303</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>304</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>305</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>306</v>
       </c>
-      <c r="L1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671.08333321759</v>
@@ -2778,7 +2781,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.124999826388</v>
@@ -2817,7 +2820,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.166666435187</v>
@@ -2856,7 +2859,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.208333333336</v>
@@ -2895,7 +2898,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.25</v>
@@ -2934,7 +2937,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.291666666664</v>
@@ -2973,7 +2976,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.333333333336</v>
@@ -3012,7 +3015,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.375</v>
@@ -3051,7 +3054,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.416666666664</v>
@@ -3090,7 +3093,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.458333333336</v>
@@ -3129,85 +3132,85 @@
         <v>230</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -3221,14 +3224,14 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6DDD9A-EF34-4108-8532-230729E9C708}">
   <dimension ref="A1:BA25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="7" customWidth="1"/>
-    <col min="2" max="5" width="11.44140625" customWidth="1"/>
-    <col min="6" max="13" width="11.109375" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
+    <col min="2" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="13" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -3242,154 +3245,154 @@
         <v>37</v>
       </c>
       <c r="E1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" t="s">
         <v>150</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>151</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>152</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>153</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>154</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>155</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>156</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>157</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>158</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>159</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>160</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>161</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>162</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>163</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>164</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>165</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>166</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>167</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>168</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>169</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>170</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>171</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>172</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>173</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>174</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>175</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>176</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>177</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>178</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>179</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>180</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>181</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>182</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>183</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>184</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>185</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>186</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>187</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>188</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>189</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>190</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>191</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>192</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>193</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>194</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>195</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>196</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>197</v>
       </c>
-      <c r="BA1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671.08333321759</v>
@@ -3551,7 +3554,7 @@
         <v>231.346451258288</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.124999826388</v>
@@ -3713,7 +3716,7 @@
         <v>230.78216691687899</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.166666435187</v>
@@ -3875,7 +3878,7 @@
         <v>235.844176498461</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.208333333336</v>
@@ -4037,7 +4040,7 @@
         <v>240.05923687940799</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.25</v>
@@ -4199,7 +4202,7 @@
         <v>242.61575673661699</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.291666666664</v>
@@ -4361,7 +4364,7 @@
         <v>241.70953129939301</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.333333333336</v>
@@ -4523,7 +4526,7 @@
         <v>236.73326993448899</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.375</v>
@@ -4685,7 +4688,7 @@
         <v>223.22249328270701</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.416666666664</v>
@@ -4847,7 +4850,7 @@
         <v>208.68241700623199</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.458333333336</v>
@@ -5009,85 +5012,85 @@
         <v>207.05273808799899</v>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -5101,14 +5104,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82624B08-6930-4D2B-BCBB-C78CE759E704}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>46</v>
       </c>
@@ -5116,7 +5119,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -5124,7 +5127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>79</v>
       </c>
@@ -5132,7 +5135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>80</v>
       </c>
@@ -5140,7 +5143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>81</v>
       </c>
@@ -5148,7 +5151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -5156,33 +5159,41 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B7">
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B8">
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>313</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>314</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>84</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -5194,14 +5205,14 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
   <dimension ref="A1:DA25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="10.33203125" customWidth="1"/>
-    <col min="5" max="7" width="11.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.28515625" customWidth="1"/>
+    <col min="5" max="7" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -5215,151 +5226,151 @@
         <v>56</v>
       </c>
       <c r="E1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F1" t="s">
         <v>199</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>200</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>201</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>202</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>203</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>204</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>205</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>206</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>207</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>208</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>209</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>210</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>211</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>212</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>213</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>214</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>215</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>216</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>217</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>218</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>219</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>220</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>221</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>222</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>223</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>224</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>225</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>226</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>227</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>228</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>229</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>230</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>231</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>232</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>233</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>234</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>235</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>236</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>237</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>238</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>239</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>240</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>241</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>242</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>243</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>244</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>245</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>246</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>247</v>
       </c>
       <c r="BB1" t="s">
         <v>57</v>
@@ -5371,154 +5382,154 @@
         <v>59</v>
       </c>
       <c r="BE1" t="s">
+        <v>247</v>
+      </c>
+      <c r="BF1" t="s">
         <v>248</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>249</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>250</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>251</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>252</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>253</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>254</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>255</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>256</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>257</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>258</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>259</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>260</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>261</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>262</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>263</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>264</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>265</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>266</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>267</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>268</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>269</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CB1" t="s">
         <v>270</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>271</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>272</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>273</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>274</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>275</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>276</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>277</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" t="s">
         <v>278</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CK1" t="s">
         <v>279</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CL1" t="s">
         <v>280</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CM1" t="s">
         <v>281</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>282</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>283</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
         <v>284</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CQ1" t="s">
         <v>285</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
         <v>286</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CS1" t="s">
         <v>287</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>288</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>289</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>290</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>291</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
         <v>292</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CY1" t="s">
         <v>293</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
         <v>294</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DA1" t="s">
         <v>295</v>
       </c>
-      <c r="DA1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="2" spans="1:105" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671.08333321759</v>
@@ -5836,7 +5847,7 @@
         <v>208.2118061324592</v>
       </c>
     </row>
-    <row r="3" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.124999826388</v>
@@ -6154,7 +6165,7 @@
         <v>207.70395022519111</v>
       </c>
     </row>
-    <row r="4" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.166666435187</v>
@@ -6472,7 +6483,7 @@
         <v>212.25975884861489</v>
       </c>
     </row>
-    <row r="5" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.208333333336</v>
@@ -6790,7 +6801,7 @@
         <v>216.0533131914672</v>
       </c>
     </row>
-    <row r="6" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.25</v>
@@ -7108,7 +7119,7 @@
         <v>218.35418106295529</v>
       </c>
     </row>
-    <row r="7" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.291666666664</v>
@@ -7426,7 +7437,7 @@
         <v>217.5385781694537</v>
       </c>
     </row>
-    <row r="8" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.333333333336</v>
@@ -7744,7 +7755,7 @@
         <v>213.05994294104011</v>
       </c>
     </row>
-    <row r="9" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.375</v>
@@ -8062,7 +8073,7 @@
         <v>200.90024395443632</v>
       </c>
     </row>
-    <row r="10" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.416666666664</v>
@@ -8380,7 +8391,7 @@
         <v>187.81417530560879</v>
       </c>
     </row>
-    <row r="11" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.458333333336</v>
@@ -8698,85 +8709,85 @@
         <v>186.3474642791991</v>
       </c>
     </row>
-    <row r="12" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:105" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -8791,12 +8802,12 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43A346A-EF8A-40F9-83B9-EC8F3EBF92E1}">
   <dimension ref="A1:BA25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -8853,145 +8864,145 @@
       <c r="AZ1"/>
       <c r="BA1"/>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.208333333336</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.25</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.291666666664</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.333333333336</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.375</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.458333333336</v>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -9005,12 +9016,12 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>46</v>
       </c>
@@ -9018,7 +9029,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -9026,7 +9037,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -9042,9 +9053,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
   <dimension ref="A1:B53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -9052,7 +9063,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -9061,7 +9072,7 @@
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -9070,7 +9081,7 @@
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -9079,441 +9090,441 @@
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B19">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B22">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B23">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B24">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B25">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B26">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B27">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B28">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B29">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B30">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B31">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B32">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B33">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B34">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B35">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B36">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B37">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B38">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B39">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B40">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B41">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B42">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B43">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B44">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B45">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B46">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B47">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B48">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B49">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B50">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B51">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B52">
         <f t="shared" si="0"/>
         <v>1.9230769230769232E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B53">
         <f t="shared" si="0"/>
@@ -9529,162 +9540,162 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671.08333321759</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.124999826388</v>
       </c>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.166666435187</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.208333333336</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.25</v>
       </c>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.291666666664</v>
       </c>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.333333333336</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.375</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.458333333336</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -9698,155 +9709,155 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD670E02-665B-45B8-BC4E-9596D2C1BC55}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.208333333336</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.25</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.291666666664</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.333333333336</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.375</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.458333333336</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -9861,14 +9872,14 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704FC51-737E-45F9-9A9E-85A96AFE5439}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>30</v>
       </c>
@@ -9882,7 +9893,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -9896,158 +9907,158 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE12AB76-2BDA-4ACA-A128-8CFB9FB6C8F8}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="7" customWidth="1"/>
-    <col min="2" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
+    <col min="2" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.208333333336</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.25</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.291666666664</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.333333333336</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.375</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.458333333336</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -10061,155 +10072,155 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FEDBA5-B0F3-4E9D-9367-08D5F5FA8AEA}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.208333333336</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.25</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.291666666664</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.333333333336</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.375</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.458333333336</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -10223,20 +10234,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A1B16B-CDA9-46BD-BA51-731AA9327652}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -10274,21 +10285,21 @@
         <v>51</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>74</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -10336,7 +10347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -10386,7 +10397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -10400,10 +10411,10 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="M8" s="6"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -10420,7 +10431,7 @@
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -10437,7 +10448,7 @@
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -10453,7 +10464,7 @@
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -10470,7 +10481,7 @@
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -10495,22 +10506,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB20090B-02A9-43B7-8D03-9C18D42920EB}">
   <dimension ref="A1:Q18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
@@ -10557,15 +10568,15 @@
         <v>44</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -10616,9 +10627,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10669,9 +10680,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10722,9 +10733,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10775,9 +10786,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10828,9 +10839,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -10881,9 +10892,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -10934,9 +10945,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -10987,9 +10998,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -11040,9 +11051,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -11093,7 +11104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -11111,7 +11122,7 @@
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -11129,7 +11140,7 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -11147,7 +11158,7 @@
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -11165,7 +11176,7 @@
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -11183,7 +11194,7 @@
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -11210,11 +11221,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6007B83A-95ED-43FB-AC05-C8A15D3323E5}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>62</v>
@@ -11231,9 +11242,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB1106B-D567-41FC-8E91-2B4CC5EC9B59}">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
@@ -11285,20 +11296,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A86A8A7-FD76-4891-A53C-CBB095359118}">
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="5"/>
+    <col min="1" max="1" width="7.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
@@ -11315,7 +11326,7 @@
         <v>13</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>19</v>
@@ -11327,18 +11338,18 @@
         <v>78</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
@@ -11362,9 +11373,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>22</v>
@@ -11394,15 +11405,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D4" s="5">
         <v>1</v>
@@ -11426,9 +11437,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>22</v>
@@ -11458,15 +11469,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D6" s="5">
         <v>1</v>
@@ -11491,9 +11502,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>22</v>
@@ -11524,15 +11535,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D8" s="5">
         <v>1</v>
@@ -11557,9 +11568,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>22</v>
@@ -11590,15 +11601,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D10" s="5">
         <v>1</v>
@@ -11623,9 +11634,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>22</v>
@@ -11656,15 +11667,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12" s="5">
         <v>1</v>
@@ -11689,9 +11700,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>22</v>
@@ -11722,15 +11733,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" s="5">
         <v>1</v>
@@ -11755,9 +11766,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>22</v>
@@ -11788,15 +11799,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D16" s="5">
         <v>1</v>
@@ -11821,9 +11832,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>22</v>
@@ -11854,15 +11865,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D18" s="5">
         <v>1</v>
@@ -11887,9 +11898,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>22</v>
@@ -11920,15 +11931,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D20" s="5">
         <v>1</v>
@@ -11953,9 +11964,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>22</v>
@@ -11995,155 +12006,155 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AEF404-3743-47D7-AC45-7AE3A9FB796E}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.208333333336</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.25</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.291666666664</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.333333333336</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.375</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.416666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.458333333336</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -12157,14 +12168,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7A97A19-79B8-46BB-9B8D-DDA080BD4E36}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>71</v>
       </c>

--- a/input_data/input_data_bidcurve_e.xlsx
+++ b/input_data/input_data_bidcurve_e.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94981EE-AB45-4040-96A6-FE8D6957E560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214AEDE7-ABC0-4D99-A194-0F490773CC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="8" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="321">
   <si>
     <t>node</t>
   </si>
@@ -1021,6 +1021,9 @@
   </si>
   <si>
     <t>inflow</t>
+  </si>
+  <si>
+    <t>deviation_penalty</t>
   </si>
 </sst>
 </file>
@@ -2208,13 +2211,13 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D94C068-DCD9-4508-A0A8-368748626A4E}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>315</v>
       </c>
@@ -2232,6 +2235,9 @@
       </c>
       <c r="F1" t="s">
         <v>319</v>
+      </c>
+      <c r="G1" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
